--- a/Plantilla VP y CAE.xlsx
+++ b/Plantilla VP y CAE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Macready\PAD 2026\Planificación y Evaluación e Competencias\Sesión 4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Macready\PAD 2026\DAV\Semana 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68FD2861-6155-4D18-BF2A-6725636D47CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FD262EB-5B5F-4146-87EF-A9865325441A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="62">
   <si>
     <t>PLANTILLA: VALOR PRESENTE (VP) – Alternativas con Vidas Económicas Iguales</t>
   </si>
@@ -223,15 +223,6 @@
   </si>
   <si>
     <t>• (A/F, i, n) = i / [(1+i)^n - 1]</t>
-  </si>
-  <si>
-    <t>RECOMENDACIÓN PEDAGÓGICA:</t>
-  </si>
-  <si>
-    <t>• Pida a los estudiantes que primero resuelvan a mano o con calculadora y luego verifiquen con la plantilla.</t>
-  </si>
-  <si>
-    <t>• Use la plantilla también para que visualicen el efecto de cambiar la tasa de interés (análisis de sensibilidad sencillo).</t>
   </si>
 </sst>
 </file>
@@ -365,7 +356,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -388,21 +379,25 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,6 +413,171 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>312421</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>944881</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>282243</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35373452-4702-4172-980B-23C826775B59}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="312421" y="60960"/>
+          <a:ext cx="632460" cy="221283"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1981200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>2613660</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38403</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14DD545C-D86A-4913-B9AA-0C376FAE32A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1981200" y="350520"/>
+          <a:ext cx="632460" cy="221283"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>45720</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>678180</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>282243</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5067BA69-D5E7-421D-BED5-FAA153D6E9BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="45720" y="60960"/>
+          <a:ext cx="632460" cy="221283"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -715,7 +875,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="13"/>
@@ -737,7 +897,7 @@
       <c r="G2" s="13"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="13"/>
@@ -763,7 +923,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="13"/>
@@ -833,7 +993,7 @@
       <c r="D13" s="7"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="14" t="s">
         <v>15</v>
       </c>
       <c r="B15" s="13"/>
@@ -923,7 +1083,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="16" t="s">
         <v>21</v>
       </c>
       <c r="B22" s="13"/>
@@ -934,7 +1094,7 @@
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="16" t="str">
+      <c r="B23" s="17" t="str">
         <f>IF(AND(B20&lt;&gt;"",C20&lt;&gt;""),IF(B20&lt;C20,"Alternativa A","Alternativa B"),"Complete los datos")</f>
         <v>Alternativa A</v>
       </c>
@@ -950,7 +1110,7 @@
       <c r="D25" s="13"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="13"/>
@@ -961,7 +1121,7 @@
       <c r="G26" s="13"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B27" s="13"/>
@@ -972,7 +1132,7 @@
       <c r="G27" s="13"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="12" t="s">
         <v>26</v>
       </c>
       <c r="B28" s="13"/>
@@ -983,7 +1143,7 @@
       <c r="G28" s="13"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="12" t="s">
         <v>27</v>
       </c>
       <c r="B29" s="13"/>
@@ -1009,6 +1169,7 @@
     <mergeCell ref="A25:D25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1023,15 +1184,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
@@ -1045,7 +1206,7 @@
       <c r="G2" s="13"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="13"/>
@@ -1068,7 +1229,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="13"/>
@@ -1126,7 +1287,7 @@
       <c r="D12" s="7"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="13"/>
@@ -1216,7 +1377,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="13"/>
@@ -1227,7 +1388,7 @@
       <c r="A22" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="16" t="str">
+      <c r="B22" s="17" t="str">
         <f>IF(AND(B19&lt;&gt;"",C19&lt;&gt;""),IF(B19&lt;C19,"Alternativa A","Alternativa B"),"Complete los datos")</f>
         <v>Alternativa A</v>
       </c>
@@ -1235,7 +1396,7 @@
       <c r="D22" s="13"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="12" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="13"/>
@@ -1246,9 +1407,8 @@
       <c r="G24" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A1:G1"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A24:G24"/>
@@ -1257,6 +1417,7 @@
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1270,7 +1431,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="13"/>
@@ -1294,7 +1455,7 @@
       <c r="H2" s="13"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="14" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="13"/>
@@ -1309,7 +1470,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="14" t="s">
         <v>36</v>
       </c>
       <c r="B7" s="13"/>
@@ -1371,7 +1532,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="14" t="s">
         <v>38</v>
       </c>
       <c r="B14" s="13"/>
@@ -1441,7 +1602,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="15" t="s">
+      <c r="A21" s="16" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="13"/>
@@ -1451,7 +1612,7 @@
       <c r="A22" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="16" t="str">
+      <c r="B22" s="17" t="str">
         <f>IF(B19&lt;C19,"Alternativa A","Alternativa B")</f>
         <v>Alternativa B</v>
       </c>
@@ -1465,7 +1626,7 @@
       <c r="C24" s="13"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="12" t="s">
         <v>44</v>
       </c>
       <c r="B25" s="13"/>
@@ -1477,7 +1638,7 @@
       <c r="H25" s="13"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="12" t="s">
         <v>45</v>
       </c>
       <c r="B26" s="13"/>
@@ -1489,7 +1650,7 @@
       <c r="H26" s="13"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="12" t="s">
         <v>46</v>
       </c>
       <c r="B27" s="13"/>
@@ -1515,6 +1676,7 @@
     <mergeCell ref="A21:C21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1533,125 +1695,131 @@
       <c r="B1" s="13"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
+      <c r="A3" s="20"/>
       <c r="B3" s="13"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="21" t="s">
         <v>48</v>
       </c>
       <c r="B4" s="13"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="20" t="s">
         <v>49</v>
       </c>
       <c r="B5" s="13"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="20" t="s">
         <v>50</v>
       </c>
       <c r="B6" s="13"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="20" t="s">
         <v>51</v>
       </c>
       <c r="B7" s="13"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="21"/>
+      <c r="A8" s="20"/>
       <c r="B8" s="13"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="21" t="s">
         <v>52</v>
       </c>
       <c r="B9" s="13"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="20" t="s">
         <v>53</v>
       </c>
       <c r="B10" s="13"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="20" t="s">
         <v>54</v>
       </c>
       <c r="B11" s="13"/>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="20" t="s">
         <v>55</v>
       </c>
       <c r="B12" s="13"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="20" t="s">
         <v>56</v>
       </c>
       <c r="B13" s="13"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="21"/>
+      <c r="A14" s="20"/>
       <c r="B14" s="13"/>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="21" t="s">
         <v>57</v>
       </c>
       <c r="B15" s="13"/>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="20" t="s">
         <v>58</v>
       </c>
       <c r="B16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="20" t="s">
         <v>59</v>
       </c>
       <c r="B17" s="13"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="20" t="s">
         <v>60</v>
       </c>
       <c r="B18" s="13"/>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="20" t="s">
         <v>61</v>
       </c>
       <c r="B19" s="13"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="21"/>
+      <c r="A20" s="20"/>
       <c r="B20" s="13"/>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="20" t="s">
-        <v>62</v>
-      </c>
+      <c r="A21" s="21"/>
       <c r="B21" s="13"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
-        <v>63</v>
-      </c>
+      <c r="A22" s="20"/>
       <c r="B22" s="13"/>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="s">
-        <v>64</v>
-      </c>
+      <c r="A23" s="20"/>
       <c r="B23" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A22:B22"/>
@@ -1662,18 +1830,6 @@
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
